--- a/TESTS/zlit_5_solovei.xlsx
+++ b/TESTS/zlit_5_solovei.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>У Китаї — при дворі великого китайського імператора</t>
+          <t>У Китаї</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -645,6 +655,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Дія у Китаї — Андерсен помістив алегоричну казку в екзотичну далеку країну</t>
+          <t>Дія у Китаї</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Про чарівний спів солов'я писали мандрівники і поети — і книга про це потрапила до імператора</t>
+          <t>Про чарівний спів солов'я писали мандрівники і поети</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Він заплакав від зворушення — спів торкнувся найглибших струн його душі</t>
+          <t>Він заплакав від зворушення</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Глибоке зворушення навіть найчерствіші серця ставали м'якшими — рибалка плакав не розуміючи чому</t>
+          <t>Глибоке зворушення навіть найчерствіші серця ставали м'якшими</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Механічного солов'я що співав заводну мелодію і був прикрашений коштовностями — всі захопились ним</t>
+          <t>Механічного солов'я що співав заводну мелодію і був прикрашений коштовностями</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Придворні вирішили що механічний кращий — він завжди однаковий і передбачуваний на відміну від «непостійного» живого</t>
+          <t>Придворні вирішили що механічний кращий</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Його забули і він повернувся у ліс — придворні і сам імператор захопились механічним злотим птахом</t>
+          <t>Його забули і він повернувся у ліс</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Яким описаний палац китайського імператора на початку казки?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бідним і малим</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Найкрасивішим у світі, з рідкісними квітами і дзвіночками на кожній квітці</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Старим і занедбаним</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Захованим у горах</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Де насправді жив соловей, чий спів так прославився?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У золотій клітці в палаці</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У темному лісі біля моря, серед простих рибаків</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У саду імператора</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У горах</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Хто, окрім придворних, вже добре знав і любив спів солов'я задовго до імператора?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніхто</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бідний рибак, що чув його щонічно і забував свою важку працю</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сусідні правителі</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише птахи в лісі</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Кого імператор послав у ліс шукати славетного солов'я?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Самого себе</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Придворних на чолі з головним управителем, які раніше навіть не чули про птаха в своєму палаці</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Рибака</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Іноземних послів</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Хто допоміг придворним розпізнати спів солов'я серед інших звуків лісу?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніхто, вони самі впізнали</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Маленька служниця з кухні, яка часто чула солов'я, провела їх до нього</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сам соловей покликав їх</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Імператор прийшов сам</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Як соловей відповів на запрошення прибути до палацу і заспівати для імператора?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Відмовився</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Скромно погодився, хоч і сказав, що його спів краще звучить у лісі</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зажадав нагороди</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Злякався і втік</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Яким був перший виступ живого солов'я перед імператором?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Невдалим</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Настільки прекрасним, що в самого імператора виступили на очах сльози</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Гучним, але байдужим</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Коротким і непомітним</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Якою «нагородою» вирішив вшанувати солов'я імператор після виступу?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Відпустив його назад у ліс</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Залишив його жити в палаці, у золотій клітці, з почесним правом гуляти лише на двох шовкових шворках</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подарував йому золото</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Призначив його радником</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Як соловей почувався, живучи в золотій клітці при дворі?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Щасливим назавжди</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сумним — він тужив за вільним лісом, хоч і виконував свій обов'язок</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Байдужим</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Гордим своїм становищем</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Звідки прибув подарунок-механічний соловей для імператора?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його зробили місцеві майстри</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його надіслав японський імператор у дарунок</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його знайшли в лісі</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його купили на ринку</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Чим механічний соловей сподобався придворним більше за живого?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Кращим співом</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він був гарно оздоблений коштовностями і завжди співав однаково, передбачувано</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був живим</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він був тихішим</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Як головний музикант пояснював «перевагу» механічного птаха над живим?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що живий птах гірше виглядає</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що в механічного птаха можна точно пояснити й передбачити кожен звук, а живий — непередбачуваний</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що механічний дешевший</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що живий птах боїться людей</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що зробив живий соловей, коли побачив, що механічна іграшка зайняла його місце?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Влаштував сварку</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тихо вилетів через відчинене вікно назад до свого лісу</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зламав механічного птаха</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Залишився жити поруч</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Як двір пояснив зникнення живого солов'я після появи механічного?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Шкодували про втрату</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Назвали його невдячним і вирішили, що механічний птах однаково кращий</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Шукали його довго</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Покарали слуг за втрату</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що сталося з механічним солов'єм через рік служби?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він співав ще краще</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його механізм зносився, і він почав ламатися та грати все рідше</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він став живим</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його замінили новим</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>У якому стані опинився імператор через кілька років після появи механічного птаха?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Здоровий і щасливий</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тяжко хворий, лежав майже мертвий, а біля його ліжка вже сиділа Смерть</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він поїхав у подорож</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він втратив трон</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому механічний соловей не міг допомогти хворому імператору, хоч його й попросили заспівати?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він заспівав чудово</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У нього не було нікого, хто б його заводив, тож він мовчав</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він заспівав, але це не сподобалось</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він заспівав надто голосно</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Хто з'явився за вікном саме тоді, коли імператору було найгірше?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лікар</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Живий соловей, що почув про хворобу свого колишнього господаря</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Механічний птах ожив</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто не з'явився</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що зробив живий соловей, заспівавши для хворого імператора і самої Смерті?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого особливого не сталось</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його спів настільки зворушив Смерть, що вона залишила імператора і пішла геть</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Соловей злякався і втік</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Імператор не почув спів</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Про що соловей попросив імператора, погоджуючись далі співати для нього?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Про золоту клітку</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Не тримати його в клітці, а дозволити прилітати вільно, коли він сам захоче</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Про нагороду</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Про трон</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Що соловей пообіцяв співати імператору замість придворних, які приховували від нього правду?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише веселі пісні</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>І про щастя, і про смуток, і про добро, і про зло в його державі — правду</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише про себе</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не пообіцяв</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яку критику Андерсен вкладав у казку «Соловей»?</t>
+          <t>Андерсен у казці «Соловей» критикує двір, що цінує штучне й показне більше за справжнє й живе.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що означає образ Смерті у фіналі казки?</t>
+          <t>Образ Смерті у фіналі казки символізує остаточну і безповоротну загибель імператора.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє рибалка у казці «Соловей»?</t>
+          <t>Рибак у казці символізує простих людей, які цінують справжню красу природи без пишноти двору.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Чому живий соловей повернувся рятувати того хто його відкинув?</t>
+          <t>Живий соловей повернувся рятувати імператора, бо пам'ятав добро і не тримав на нього зла.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка головна думка казки «Соловей»?</t>
+          <t>Головна думка казки — справжнє живе мистецтво цінніше за досконалу, але штучну імітацію.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що символізує протиставлення живого і механічного солов'я?</t>
+          <t>Протиставлення живого і механічного солов'я в казці нічого не символізує, це лише розважальний сюжет.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває казка «Соловей»?</t>
+          <t>Що сталося після того, як механічний соловей зайняв місце живого?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Справжня і штучна краса</t>
+          <t>Живий соловей тихо повернувся в ліс</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Вдячність і відданість</t>
+          <t>Механічний птах зрештою зламався</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Небезпека механізмів</t>
+          <t>Імператор одразу одужав</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Цінність живого мистецтва</t>
+          <t>Живий соловей повернувся врятувати хворого імператора</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Він зламався — механізм від надмірного використання вийшов з ладу і лише один раз на рік міг співати</t>
+          <t>Він зламався</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Він важко захворів і смерть вже стояла біля його ліжка — не було музики що могла б розрадити</t>
+          <t>Він важко захворів і смерть вже стояла біля його ліжка</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Живий соловей — почувши про хворобу він прилетів і своїм співом прогнав Смерть і повернув здоров'я</t>
+          <t>Живий соловей</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
